--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/42.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/42.xlsx
@@ -426,13 +426,13 @@
         <v>-8.293987187512418</v>
       </c>
       <c r="E2">
-        <v>-10.35082115704588</v>
+        <v>-19.03793775712818</v>
       </c>
       <c r="F2">
-        <v>-2.682920633271561</v>
+        <v>-4.49248011264565</v>
       </c>
       <c r="G2">
-        <v>-5.789714335057117</v>
+        <v>-12.42230340844436</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.726800857129248</v>
       </c>
       <c r="E3">
-        <v>-12.02761545565805</v>
+        <v>-19.56465815438234</v>
       </c>
       <c r="F3">
-        <v>-2.710947615977879</v>
+        <v>-4.847916826206265</v>
       </c>
       <c r="G3">
-        <v>-6.378175171971051</v>
+        <v>-11.52193293131117</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.187858062690585</v>
       </c>
       <c r="E4">
-        <v>-11.53505333784374</v>
+        <v>-20.83849977884398</v>
       </c>
       <c r="F4">
-        <v>-2.649462873872488</v>
+        <v>-4.152719423815613</v>
       </c>
       <c r="G4">
-        <v>-6.609078014330735</v>
+        <v>-12.34105051896783</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.593123699869945</v>
       </c>
       <c r="E5">
-        <v>-11.917772790128</v>
+        <v>-20.48285607265159</v>
       </c>
       <c r="F5">
-        <v>-2.326649753736327</v>
+        <v>-4.272947011923128</v>
       </c>
       <c r="G5">
-        <v>-6.07244735316979</v>
+        <v>-11.80942043946348</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.943385052769843</v>
       </c>
       <c r="E6">
-        <v>-12.96457031326707</v>
+        <v>-20.76796426770051</v>
       </c>
       <c r="F6">
-        <v>-2.318052956830074</v>
+        <v>-4.261923926894075</v>
       </c>
       <c r="G6">
-        <v>-5.900337438712236</v>
+        <v>-12.14214614925585</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.22167959537992</v>
       </c>
       <c r="E7">
-        <v>-13.60814345381516</v>
+        <v>-22.43544349527889</v>
       </c>
       <c r="F7">
-        <v>-2.438622660674944</v>
+        <v>-3.671245781551651</v>
       </c>
       <c r="G7">
-        <v>-5.470736943598817</v>
+        <v>-11.93314546080546</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.41780108567026</v>
       </c>
       <c r="E8">
-        <v>-13.84063078089494</v>
+        <v>-23.47640381542208</v>
       </c>
       <c r="F8">
-        <v>-2.076781010355884</v>
+        <v>-3.99678920064744</v>
       </c>
       <c r="G8">
-        <v>-6.166034354488272</v>
+        <v>-12.20520466518526</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.53135530480887</v>
       </c>
       <c r="E9">
-        <v>-14.77157182502178</v>
+        <v>-24.74520071983917</v>
       </c>
       <c r="F9">
-        <v>-2.2722558365989</v>
+        <v>-4.04890593579457</v>
       </c>
       <c r="G9">
-        <v>-5.741670688983727</v>
+        <v>-11.25858865139325</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.5576860739871</v>
       </c>
       <c r="E10">
-        <v>-15.71547336175857</v>
+        <v>-24.36688294429038</v>
       </c>
       <c r="F10">
-        <v>-2.284898379900426</v>
+        <v>-4.428745524674256</v>
       </c>
       <c r="G10">
-        <v>-5.484058703130163</v>
+        <v>-10.41580033140676</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.49778568027738</v>
       </c>
       <c r="E11">
-        <v>-16.19846681399466</v>
+        <v>-25.68979964157314</v>
       </c>
       <c r="F11">
-        <v>-1.976851737086568</v>
+        <v>-3.392505949081436</v>
       </c>
       <c r="G11">
-        <v>-5.133581584701195</v>
+        <v>-11.37934416722394</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.35805463837258</v>
       </c>
       <c r="E12">
-        <v>-16.2822073553445</v>
+        <v>-25.3812973498006</v>
       </c>
       <c r="F12">
-        <v>-1.877686218562634</v>
+        <v>-3.902159822021235</v>
       </c>
       <c r="G12">
-        <v>-3.86670522182115</v>
+        <v>-10.06738053889556</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.14145969713672</v>
       </c>
       <c r="E13">
-        <v>-16.27379345063825</v>
+        <v>-23.77989761494214</v>
       </c>
       <c r="F13">
-        <v>-1.978650951085449</v>
+        <v>-3.287414290157875</v>
       </c>
       <c r="G13">
-        <v>-3.988212137388947</v>
+        <v>-8.816135915524713</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.874465971681479</v>
       </c>
       <c r="E14">
-        <v>-18.77700708480621</v>
+        <v>-26.10617924115641</v>
       </c>
       <c r="F14">
-        <v>-1.833456369457557</v>
+        <v>-3.201235915775031</v>
       </c>
       <c r="G14">
-        <v>-2.967227236952129</v>
+        <v>-9.361658687111753</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.576457090057291</v>
       </c>
       <c r="E15">
-        <v>-18.39038408792734</v>
+        <v>-27.04230538802202</v>
       </c>
       <c r="F15">
-        <v>-1.507608111157538</v>
+        <v>-3.083193560876101</v>
       </c>
       <c r="G15">
-        <v>-3.094007075565954</v>
+        <v>-8.292203581798818</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.277510311093419</v>
       </c>
       <c r="E16">
-        <v>-19.68161505257844</v>
+        <v>-26.95782217693493</v>
       </c>
       <c r="F16">
-        <v>-0.9038069694199643</v>
+        <v>-3.525653583570415</v>
       </c>
       <c r="G16">
-        <v>-2.753734556186858</v>
+        <v>-7.939974291057107</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.002220291262883</v>
       </c>
       <c r="E17">
-        <v>-20.22431643460567</v>
+        <v>-27.49414293908535</v>
       </c>
       <c r="F17">
-        <v>-1.14690629438473</v>
+        <v>-2.84183546419202</v>
       </c>
       <c r="G17">
-        <v>-1.97745003476719</v>
+        <v>-8.087744103986699</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.757490182063835</v>
       </c>
       <c r="E18">
-        <v>-20.83825071277356</v>
+        <v>-28.77814193074619</v>
       </c>
       <c r="F18">
-        <v>-0.6884902587776917</v>
+        <v>-2.02190581175743</v>
       </c>
       <c r="G18">
-        <v>-2.038516849210016</v>
+        <v>-7.23446899989622</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.552685078535609</v>
       </c>
       <c r="E19">
-        <v>-21.8223922695425</v>
+        <v>-29.84061703089982</v>
       </c>
       <c r="F19">
-        <v>-0.5679089577891816</v>
+        <v>-2.702625837049355</v>
       </c>
       <c r="G19">
-        <v>-0.472914794336564</v>
+        <v>-6.09744369900964</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.372607234177941</v>
       </c>
       <c r="E20">
-        <v>-23.01124802230219</v>
+        <v>-30.72871418244009</v>
       </c>
       <c r="F20">
-        <v>0.1016297642997552</v>
+        <v>-2.612533426688284</v>
       </c>
       <c r="G20">
-        <v>-1.343839589195297</v>
+        <v>-8.014392396025313</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.209009274533845</v>
       </c>
       <c r="E21">
-        <v>-22.78841087333275</v>
+        <v>-29.85480700420286</v>
       </c>
       <c r="F21">
-        <v>0.1918505716082606</v>
+        <v>-2.00160418344962</v>
       </c>
       <c r="G21">
-        <v>-1.202264722569935</v>
+        <v>-6.794936247122362</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.051734165333468</v>
       </c>
       <c r="E22">
-        <v>-23.85776472550403</v>
+        <v>-28.67574407648475</v>
       </c>
       <c r="F22">
-        <v>0.515598918542183</v>
+        <v>-2.16057202988386</v>
       </c>
       <c r="G22">
-        <v>-1.511552666763194</v>
+        <v>-6.836896508424541</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.889503746924317</v>
       </c>
       <c r="E23">
-        <v>-24.47364171902121</v>
+        <v>-31.09786632659736</v>
       </c>
       <c r="F23">
-        <v>0.5019159457827407</v>
+        <v>-2.000147085188096</v>
       </c>
       <c r="G23">
-        <v>-1.350454531859137</v>
+        <v>-7.366006609771239</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.73004224825614</v>
       </c>
       <c r="E24">
-        <v>-24.36669274838205</v>
+        <v>-31.90246068167318</v>
       </c>
       <c r="F24">
-        <v>0.6812185552209021</v>
+        <v>-1.435404294859922</v>
       </c>
       <c r="G24">
-        <v>-1.444110438830368</v>
+        <v>-6.995848724428722</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.573254437938659</v>
       </c>
       <c r="E25">
-        <v>-25.25576805030797</v>
+        <v>-30.15965481745121</v>
       </c>
       <c r="F25">
-        <v>0.922914625805325</v>
+        <v>-1.991115395395373</v>
       </c>
       <c r="G25">
-        <v>-1.706949410628127</v>
+        <v>-6.059726057183823</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.438321772087058</v>
       </c>
       <c r="E26">
-        <v>-24.38026005650903</v>
+        <v>-31.60447803502046</v>
       </c>
       <c r="F26">
-        <v>1.244531583411844</v>
+        <v>-1.599556892868283</v>
       </c>
       <c r="G26">
-        <v>-1.531643586371674</v>
+        <v>-5.817847528707796</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.337581205202826</v>
       </c>
       <c r="E27">
-        <v>-25.42721607623838</v>
+        <v>-30.54602648402265</v>
       </c>
       <c r="F27">
-        <v>1.270663261500558</v>
+        <v>-0.9706794131131629</v>
       </c>
       <c r="G27">
-        <v>-1.767510916950798</v>
+        <v>-7.133023472942868</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.276852687132939</v>
       </c>
       <c r="E28">
-        <v>-24.77908276236456</v>
+        <v>-30.71453553032207</v>
       </c>
       <c r="F28">
-        <v>1.025827678459524</v>
+        <v>-0.6442769770206709</v>
       </c>
       <c r="G28">
-        <v>-2.458066962686855</v>
+        <v>-7.611783229459887</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.264412655569718</v>
       </c>
       <c r="E29">
-        <v>-24.25228990952628</v>
+        <v>-30.48872543816659</v>
       </c>
       <c r="F29">
-        <v>1.106984489646598</v>
+        <v>-1.857825281713113</v>
       </c>
       <c r="G29">
-        <v>-2.154583499432253</v>
+        <v>-8.364725140705666</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.289322322106034</v>
       </c>
       <c r="E30">
-        <v>-23.46312180115758</v>
+        <v>-32.05005949924219</v>
       </c>
       <c r="F30">
-        <v>1.180401035821912</v>
+        <v>-1.713607345253122</v>
       </c>
       <c r="G30">
-        <v>-2.403782433207402</v>
+        <v>-8.197149874443264</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.345852788902688</v>
       </c>
       <c r="E31">
-        <v>-24.14640060180492</v>
+        <v>-31.10659948872115</v>
       </c>
       <c r="F31">
-        <v>1.301138898249551</v>
+        <v>-1.04774823116742</v>
       </c>
       <c r="G31">
-        <v>-2.101877237522893</v>
+        <v>-6.798771995125353</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.413450822561588</v>
       </c>
       <c r="E32">
-        <v>-23.3202575031636</v>
+        <v>-29.87093516438117</v>
       </c>
       <c r="F32">
-        <v>0.7957999911109352</v>
+        <v>-1.086999592181672</v>
       </c>
       <c r="G32">
-        <v>-2.184006213155794</v>
+        <v>-7.584850962899965</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.46840462347316</v>
       </c>
       <c r="E33">
-        <v>-23.94083052422673</v>
+        <v>-30.52809146271527</v>
       </c>
       <c r="F33">
-        <v>0.8879343271199075</v>
+        <v>-1.223669444867354</v>
       </c>
       <c r="G33">
-        <v>-2.60038666660621</v>
+        <v>-7.840937180728386</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.493139969618499</v>
       </c>
       <c r="E34">
-        <v>-22.62198039660285</v>
+        <v>-28.48756786757002</v>
       </c>
       <c r="F34">
-        <v>0.9518876040856405</v>
+        <v>-1.026778938732954</v>
       </c>
       <c r="G34">
-        <v>-2.370632251792332</v>
+        <v>-7.543609289119304</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.465355111188221</v>
       </c>
       <c r="E35">
-        <v>-22.19685631371077</v>
+        <v>-29.05492226209501</v>
       </c>
       <c r="F35">
-        <v>1.028619276606959</v>
+        <v>-1.960438465367499</v>
       </c>
       <c r="G35">
-        <v>-2.312029634740649</v>
+        <v>-7.725241308542365</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.381529474237608</v>
       </c>
       <c r="E36">
-        <v>-21.73096237932764</v>
+        <v>-28.54359414799292</v>
       </c>
       <c r="F36">
-        <v>0.8304787640617338</v>
+        <v>-1.902088265514302</v>
       </c>
       <c r="G36">
-        <v>-1.777712234779112</v>
+        <v>-6.867359369382426</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.23735770458867</v>
       </c>
       <c r="E37">
-        <v>-22.32888850187841</v>
+        <v>-30.84605600092684</v>
       </c>
       <c r="F37">
-        <v>0.8091284226219794</v>
+        <v>-2.001684535087692</v>
       </c>
       <c r="G37">
-        <v>-1.773154618033043</v>
+        <v>-8.915652084201112</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.037219732937637</v>
       </c>
       <c r="E38">
-        <v>-21.06666694172045</v>
+        <v>-27.70905978701538</v>
       </c>
       <c r="F38">
-        <v>0.9975704096152277</v>
+        <v>-2.366833856446131</v>
       </c>
       <c r="G38">
-        <v>-2.046066940018298</v>
+        <v>-8.322620505654871</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.795421786811783</v>
       </c>
       <c r="E39">
-        <v>-20.20697237915629</v>
+        <v>-27.72350109062584</v>
       </c>
       <c r="F39">
-        <v>0.4242946066708158</v>
+        <v>-2.045124121690498</v>
       </c>
       <c r="G39">
-        <v>-2.165037471320645</v>
+        <v>-7.257201302860053</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.522630577360383</v>
       </c>
       <c r="E40">
-        <v>-20.35372210784886</v>
+        <v>-27.14788223103685</v>
       </c>
       <c r="F40">
-        <v>0.8488188183597148</v>
+        <v>-1.550488549763454</v>
       </c>
       <c r="G40">
-        <v>-0.8917135080762902</v>
+        <v>-8.219222651873649</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.242829163198865</v>
       </c>
       <c r="E41">
-        <v>-19.32867484536863</v>
+        <v>-25.69171518607839</v>
       </c>
       <c r="F41">
-        <v>0.410907361074173</v>
+        <v>-1.618195159431272</v>
       </c>
       <c r="G41">
-        <v>-0.9531478193337737</v>
+        <v>-8.116805883338701</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.971130731885117</v>
       </c>
       <c r="E42">
-        <v>-19.33289085466977</v>
+        <v>-26.27366032385609</v>
       </c>
       <c r="F42">
-        <v>0.7048667878360224</v>
+        <v>-1.054931833284498</v>
       </c>
       <c r="G42">
-        <v>-0.799166653992152</v>
+        <v>-7.312630978663752</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.722496730145387</v>
       </c>
       <c r="E43">
-        <v>-18.37938895303672</v>
+        <v>-26.26325389058646</v>
       </c>
       <c r="F43">
-        <v>0.4826232689715402</v>
+        <v>-2.062578651234886</v>
       </c>
       <c r="G43">
-        <v>-0.39730232472072</v>
+        <v>-7.75564838873374</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.509132128576852</v>
       </c>
       <c r="E44">
-        <v>-18.92905512808775</v>
+        <v>-24.90752839911812</v>
       </c>
       <c r="F44">
-        <v>0.2258070081838179</v>
+        <v>-1.896279753285872</v>
       </c>
       <c r="G44">
-        <v>-0.04447913287674857</v>
+        <v>-7.83346583923753</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.329342270854641</v>
       </c>
       <c r="E45">
-        <v>-18.18995382834786</v>
+        <v>-25.57615758635065</v>
       </c>
       <c r="F45">
-        <v>0.2149984703120899</v>
+        <v>-1.738490673665816</v>
       </c>
       <c r="G45">
-        <v>-0.7217790435126484</v>
+        <v>-9.134191283724808</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.187575217402305</v>
       </c>
       <c r="E46">
-        <v>-17.0311716714731</v>
+        <v>-25.80450135971342</v>
       </c>
       <c r="F46">
-        <v>0.7477977568535096</v>
+        <v>-1.708960204123417</v>
       </c>
       <c r="G46">
-        <v>-0.3429751393609938</v>
+        <v>-7.107669473953038</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.075314843076995</v>
       </c>
       <c r="E47">
-        <v>-16.86009498041133</v>
+        <v>-24.22941205883953</v>
       </c>
       <c r="F47">
-        <v>0.4642666473255032</v>
+        <v>-1.318635969026498</v>
       </c>
       <c r="G47">
-        <v>-0.2890252944806038</v>
+        <v>-7.004360213153921</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.986497448454687</v>
       </c>
       <c r="E48">
-        <v>-16.18600445352555</v>
+        <v>-24.21485754337888</v>
       </c>
       <c r="F48">
-        <v>0.3786018607323951</v>
+        <v>-1.058129331459304</v>
       </c>
       <c r="G48">
-        <v>-0.6088820533168341</v>
+        <v>-7.028746251783715</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.913880610612988</v>
       </c>
       <c r="E49">
-        <v>-15.65276758217435</v>
+        <v>-24.6443199043703</v>
       </c>
       <c r="F49">
-        <v>0.5477254915249562</v>
+        <v>-2.208307529837584</v>
       </c>
       <c r="G49">
-        <v>-0.1172500646221135</v>
+        <v>-6.662650518731789</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.842439352543903</v>
       </c>
       <c r="E50">
-        <v>-14.87749283206119</v>
+        <v>-24.24708216441746</v>
       </c>
       <c r="F50">
-        <v>0.2211548968496959</v>
+        <v>-1.727014471667432</v>
       </c>
       <c r="G50">
-        <v>-0.1971871842533056</v>
+        <v>-8.127092512927559</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.767027872463662</v>
       </c>
       <c r="E51">
-        <v>-14.48540849552907</v>
+        <v>-22.17772351102836</v>
       </c>
       <c r="F51">
-        <v>0.2965363305044509</v>
+        <v>-2.221268166221785</v>
       </c>
       <c r="G51">
-        <v>0.006842453534526228</v>
+        <v>-7.588105934686934</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.675671826556612</v>
       </c>
       <c r="E52">
-        <v>-14.78016686868834</v>
+        <v>-21.8636013830123</v>
       </c>
       <c r="F52">
-        <v>0.386753824343345</v>
+        <v>-2.021798952362469</v>
       </c>
       <c r="G52">
-        <v>0.4603269603791426</v>
+        <v>-6.745826204042153</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.56613573216776</v>
       </c>
       <c r="E53">
-        <v>-12.61111838849439</v>
+        <v>-21.69686297004988</v>
       </c>
       <c r="F53">
-        <v>0.313066402027315</v>
+        <v>-1.966489689244949</v>
       </c>
       <c r="G53">
-        <v>-0.2896224768044227</v>
+        <v>-7.764432218848373</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.439623999722756</v>
       </c>
       <c r="E54">
-        <v>-12.82355363266821</v>
+        <v>-20.36117597606549</v>
       </c>
       <c r="F54">
-        <v>0.1181747464358697</v>
+        <v>-1.498587190141051</v>
       </c>
       <c r="G54">
-        <v>-0.4945610129642208</v>
+        <v>-7.33787341612056</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.297619119825765</v>
       </c>
       <c r="E55">
-        <v>-12.56001455931783</v>
+        <v>-21.84111298109021</v>
       </c>
       <c r="F55">
-        <v>0.4910759299497064</v>
+        <v>-2.29994898724189</v>
       </c>
       <c r="G55">
-        <v>-0.4984098858534494</v>
+        <v>-7.503824477711037</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.152294269823026</v>
       </c>
       <c r="E56">
-        <v>-12.10985707211135</v>
+        <v>-20.48595807734684</v>
       </c>
       <c r="F56">
-        <v>0.2685143180025492</v>
+        <v>-2.003452271125266</v>
       </c>
       <c r="G56">
-        <v>-0.5087818272028541</v>
+        <v>-8.001215010242582</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.010588880663777</v>
       </c>
       <c r="E57">
-        <v>-11.5018505664195</v>
+        <v>-19.93915842634267</v>
       </c>
       <c r="F57">
-        <v>0.40392919407299</v>
+        <v>-1.501277727465344</v>
       </c>
       <c r="G57">
-        <v>-1.058304407870858</v>
+        <v>-7.695254224710601</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.887679702881608</v>
       </c>
       <c r="E58">
-        <v>-11.55736060080553</v>
+        <v>-20.12199103592835</v>
       </c>
       <c r="F58">
-        <v>0.3425380574841158</v>
+        <v>-1.891881950744409</v>
       </c>
       <c r="G58">
-        <v>-1.189172648547751</v>
+        <v>-8.016101912457783</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.794050493476755</v>
       </c>
       <c r="E59">
-        <v>-10.43725161195628</v>
+        <v>-20.17602931626188</v>
       </c>
       <c r="F59">
-        <v>0.6379578959771007</v>
+        <v>-2.05012828917081</v>
       </c>
       <c r="G59">
-        <v>-1.586754983684108</v>
+        <v>-8.406140719228977</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.736546993664632</v>
       </c>
       <c r="E60">
-        <v>-10.80357345985876</v>
+        <v>-19.68103540790546</v>
       </c>
       <c r="F60">
-        <v>0.5197581512716393</v>
+        <v>-1.541486681197232</v>
       </c>
       <c r="G60">
-        <v>-1.958924257842565</v>
+        <v>-9.079621287969683</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.724416857857748</v>
       </c>
       <c r="E61">
-        <v>-9.841118765112547</v>
+        <v>-18.28610691695272</v>
       </c>
       <c r="F61">
-        <v>0.5375639085948146</v>
+        <v>-1.916515940568861</v>
       </c>
       <c r="G61">
-        <v>-1.942025966811425</v>
+        <v>-9.166517878528458</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.754870602023727</v>
       </c>
       <c r="E62">
-        <v>-9.962604137316319</v>
+        <v>-18.59534734998851</v>
       </c>
       <c r="F62">
-        <v>0.261098773012688</v>
+        <v>-1.169552202442462</v>
       </c>
       <c r="G62">
-        <v>-1.811325068434064</v>
+        <v>-9.551615165631127</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.830126701354521</v>
       </c>
       <c r="E63">
-        <v>-9.567277413394713</v>
+        <v>-18.34526237291492</v>
       </c>
       <c r="F63">
-        <v>0.1942495236067679</v>
+        <v>-1.988126645806072</v>
       </c>
       <c r="G63">
-        <v>-1.837046564238551</v>
+        <v>-9.154170641800267</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.943119139460843</v>
       </c>
       <c r="E64">
-        <v>-9.953918524169607</v>
+        <v>-17.84426823649833</v>
       </c>
       <c r="F64">
-        <v>0.05012602103069593</v>
+        <v>-2.282853969150317</v>
       </c>
       <c r="G64">
-        <v>-3.096605803041034</v>
+        <v>-9.796660072912017</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.08540673522687</v>
       </c>
       <c r="E65">
-        <v>-9.550155253171711</v>
+        <v>-16.832154295784</v>
       </c>
       <c r="F65">
-        <v>0.3227177106373321</v>
+        <v>-2.184530071907627</v>
       </c>
       <c r="G65">
-        <v>-2.511189939734265</v>
+        <v>-10.47569574975286</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.25062113710786</v>
       </c>
       <c r="E66">
-        <v>-10.04014972622367</v>
+        <v>-17.50487722351947</v>
       </c>
       <c r="F66">
-        <v>0.07111850775244101</v>
+        <v>-2.022866717944678</v>
       </c>
       <c r="G66">
-        <v>-2.3979976395981</v>
+        <v>-10.2494030236842</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.424931649856846</v>
       </c>
       <c r="E67">
-        <v>-9.203215274022062</v>
+        <v>-18.51290195220487</v>
       </c>
       <c r="F67">
-        <v>-0.2626108380178126</v>
+        <v>-2.159071028149987</v>
       </c>
       <c r="G67">
-        <v>-2.602647428260667</v>
+        <v>-8.850057184006252</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.604060312805532</v>
       </c>
       <c r="E68">
-        <v>-9.560819809459774</v>
+        <v>-18.59047471195626</v>
       </c>
       <c r="F68">
-        <v>-0.02376186619681157</v>
+        <v>-2.392682232883086</v>
       </c>
       <c r="G68">
-        <v>-2.740229048248184</v>
+        <v>-9.381516639989513</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.778083902823217</v>
       </c>
       <c r="E69">
-        <v>-8.670381436857545</v>
+        <v>-17.52977930208765</v>
       </c>
       <c r="F69">
-        <v>-0.2478087408971883</v>
+        <v>-2.422047028944926</v>
       </c>
       <c r="G69">
-        <v>-3.205683451341655</v>
+        <v>-9.791961363638892</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.94207236965333</v>
       </c>
       <c r="E70">
-        <v>-9.22044158914724</v>
+        <v>-17.17361934985838</v>
       </c>
       <c r="F70">
-        <v>-0.2925836557533071</v>
+        <v>-2.854059681955133</v>
       </c>
       <c r="G70">
-        <v>-2.512971643041043</v>
+        <v>-10.6958821224994</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.094387625845364</v>
       </c>
       <c r="E71">
-        <v>-9.203754162428975</v>
+        <v>-18.59113586916138</v>
       </c>
       <c r="F71">
-        <v>-0.389396610853291</v>
+        <v>-3.049059025308942</v>
       </c>
       <c r="G71">
-        <v>-2.909353051086643</v>
+        <v>-9.460935326614313</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.229629674659432</v>
       </c>
       <c r="E72">
-        <v>-8.997015738556799</v>
+        <v>-19.68612541269008</v>
       </c>
       <c r="F72">
-        <v>-0.6597152603066452</v>
+        <v>-3.22073237096732</v>
       </c>
       <c r="G72">
-        <v>-2.539533131564748</v>
+        <v>-9.181116033246427</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.351623234945993</v>
       </c>
       <c r="E73">
-        <v>-9.823584513754847</v>
+        <v>-17.86110510285885</v>
       </c>
       <c r="F73">
-        <v>-0.783606717436742</v>
+        <v>-2.613224285102218</v>
       </c>
       <c r="G73">
-        <v>-3.294949083866348</v>
+        <v>-9.686614464251361</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.457460168712001</v>
       </c>
       <c r="E74">
-        <v>-10.33105889647641</v>
+        <v>-17.2125370554803</v>
       </c>
       <c r="F74">
-        <v>-0.4588461055365987</v>
+        <v>-2.729796287861179</v>
       </c>
       <c r="G74">
-        <v>-2.709401971697201</v>
+        <v>-10.51737710722249</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.55001501986131</v>
       </c>
       <c r="E75">
-        <v>-10.59069442523218</v>
+        <v>-18.41103845787633</v>
       </c>
       <c r="F75">
-        <v>-0.6320486174205445</v>
+        <v>-2.485274656065807</v>
       </c>
       <c r="G75">
-        <v>-2.534775360303553</v>
+        <v>-7.883799777959413</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.633085196227221</v>
       </c>
       <c r="E76">
-        <v>-11.22255240352243</v>
+        <v>-19.92657379707535</v>
       </c>
       <c r="F76">
-        <v>-0.7184125461016154</v>
+        <v>-3.238527359514259</v>
       </c>
       <c r="G76">
-        <v>-2.538112362629509</v>
+        <v>-7.69897841118057</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.706493714849429</v>
       </c>
       <c r="E77">
-        <v>-10.54966645072269</v>
+        <v>-20.31361794203693</v>
       </c>
       <c r="F77">
-        <v>-1.30004243430326</v>
+        <v>-3.855125120890279</v>
       </c>
       <c r="G77">
-        <v>-2.334804593584755</v>
+        <v>-8.605957268534482</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.778658526087267</v>
       </c>
       <c r="E78">
-        <v>-11.54252984843041</v>
+        <v>-19.49069911688906</v>
       </c>
       <c r="F78">
-        <v>-1.005917334060851</v>
+        <v>-2.396752001933041</v>
       </c>
       <c r="G78">
-        <v>-2.009471475965811</v>
+        <v>-10.35894004300314</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.848890216613431</v>
       </c>
       <c r="E79">
-        <v>-11.34925910625704</v>
+        <v>-21.20228568130216</v>
       </c>
       <c r="F79">
-        <v>-1.142261638357233</v>
+        <v>-3.157585095484511</v>
       </c>
       <c r="G79">
-        <v>-1.52304350466437</v>
+        <v>-10.0220209320578</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.921168942620586</v>
       </c>
       <c r="E80">
-        <v>-13.17002717899507</v>
+        <v>-21.29304535736389</v>
       </c>
       <c r="F80">
-        <v>-1.38162419796797</v>
+        <v>-3.344978369345815</v>
       </c>
       <c r="G80">
-        <v>-2.032449870546603</v>
+        <v>-10.69189871952624</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.996789315039319</v>
       </c>
       <c r="E81">
-        <v>-12.74160636702541</v>
+        <v>-21.42053548610183</v>
       </c>
       <c r="F81">
-        <v>-1.49645911428326</v>
+        <v>-3.171869462978385</v>
       </c>
       <c r="G81">
-        <v>-1.204535327889071</v>
+        <v>-8.49765398852189</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.070847838009938</v>
       </c>
       <c r="E82">
-        <v>-13.75438146494485</v>
+        <v>-21.88520220402889</v>
       </c>
       <c r="F82">
-        <v>-1.345734351874278</v>
+        <v>-3.807309269298484</v>
       </c>
       <c r="G82">
-        <v>-1.889424703991967</v>
+        <v>-7.772307150591041</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.144664460667604</v>
       </c>
       <c r="E83">
-        <v>-14.58028455446378</v>
+        <v>-24.23740028698906</v>
       </c>
       <c r="F83">
-        <v>-1.338987299378476</v>
+        <v>-3.985655114386411</v>
       </c>
       <c r="G83">
-        <v>-1.950163396278848</v>
+        <v>-6.530335259347181</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.208246675277501</v>
       </c>
       <c r="E84">
-        <v>-15.64291362273366</v>
+        <v>-23.59299390722356</v>
       </c>
       <c r="F84">
-        <v>-1.817332197962065</v>
+        <v>-3.712801660680491</v>
       </c>
       <c r="G84">
-        <v>-1.283822765651493</v>
+        <v>-7.596236801711237</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.257489206877782</v>
       </c>
       <c r="E85">
-        <v>-17.15802328537596</v>
+        <v>-24.84638947154057</v>
       </c>
       <c r="F85">
-        <v>-1.797897041957583</v>
+        <v>-3.31139552646892</v>
       </c>
       <c r="G85">
-        <v>0.07909823349505832</v>
+        <v>-6.652984040017665</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.285909445852683</v>
       </c>
       <c r="E86">
-        <v>-17.790940926584</v>
+        <v>-26.79400915818146</v>
       </c>
       <c r="F86">
-        <v>-1.961192279704046</v>
+        <v>-3.842473465547322</v>
       </c>
       <c r="G86">
-        <v>-0.3254402913473212</v>
+        <v>-5.824790593527581</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.283772281631452</v>
       </c>
       <c r="E87">
-        <v>-19.00077709942123</v>
+        <v>-26.04480030445644</v>
       </c>
       <c r="F87">
-        <v>-1.903691984806122</v>
+        <v>-3.476789847214078</v>
       </c>
       <c r="G87">
-        <v>-0.5438482420086399</v>
+        <v>-6.954009868324242</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.250358508370967</v>
       </c>
       <c r="E88">
-        <v>-20.78907148505026</v>
+        <v>-27.92976855320121</v>
       </c>
       <c r="F88">
-        <v>-2.248679671947823</v>
+        <v>-4.032602836940073</v>
       </c>
       <c r="G88">
-        <v>-0.2846940820221368</v>
+        <v>-6.349946822895149</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.17910772439042</v>
       </c>
       <c r="E89">
-        <v>-21.99091942973795</v>
+        <v>-28.04005500918402</v>
       </c>
       <c r="F89">
-        <v>-2.116622168960929</v>
+        <v>-3.986887725081777</v>
       </c>
       <c r="G89">
-        <v>-0.046946611489451</v>
+        <v>-5.43662536426683</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.075388449149226</v>
       </c>
       <c r="E90">
-        <v>-23.50530906501304</v>
+        <v>-30.44523397379692</v>
       </c>
       <c r="F90">
-        <v>-2.186564542248902</v>
+        <v>-4.029103813030648</v>
       </c>
       <c r="G90">
-        <v>0.1660440423772244</v>
+        <v>-7.383216616850527</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.94511691209151</v>
       </c>
       <c r="E91">
-        <v>-25.06720692110259</v>
+        <v>-31.37560443019879</v>
       </c>
       <c r="F91">
-        <v>-2.381842217050052</v>
+        <v>-3.558708756411727</v>
       </c>
       <c r="G91">
-        <v>0.0923642122598933</v>
+        <v>-6.15068151881163</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.796172610006145</v>
       </c>
       <c r="E92">
-        <v>-27.29400703031636</v>
+        <v>-32.20286379768301</v>
       </c>
       <c r="F92">
-        <v>-2.832879984200355</v>
+        <v>-3.956750890600528</v>
       </c>
       <c r="G92">
-        <v>0.003151079280150923</v>
+        <v>-6.989522529262112</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.646474365733404</v>
       </c>
       <c r="E93">
-        <v>-30.18817967522552</v>
+        <v>-35.10624735872378</v>
       </c>
       <c r="F93">
-        <v>-2.83319807728303</v>
+        <v>-2.742143103999906</v>
       </c>
       <c r="G93">
-        <v>0.2007167105958767</v>
+        <v>-7.395711508548892</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.505138535857599</v>
       </c>
       <c r="E94">
-        <v>-31.2200445553243</v>
+        <v>-37.41350486563183</v>
       </c>
       <c r="F94">
-        <v>-2.804191964306602</v>
+        <v>-4.270109853568539</v>
       </c>
       <c r="G94">
-        <v>-0.1328489919157136</v>
+        <v>-7.148980053386447</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.389642823117641</v>
       </c>
       <c r="E95">
-        <v>-34.08135406435981</v>
+        <v>-37.61725223242193</v>
       </c>
       <c r="F95">
-        <v>-3.059000262509939</v>
+        <v>-4.3571513867851</v>
       </c>
       <c r="G95">
-        <v>0.01347052108460455</v>
+        <v>-7.528049736484417</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.309053898337486</v>
       </c>
       <c r="E96">
-        <v>-36.07576420868495</v>
+        <v>-40.70433107734685</v>
       </c>
       <c r="F96">
-        <v>-2.97558117994582</v>
+        <v>-4.463075554948476</v>
       </c>
       <c r="G96">
-        <v>-0.8123538834395604</v>
+        <v>-6.897418640088499</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.266403242900046</v>
       </c>
       <c r="E97">
-        <v>-38.50380743856259</v>
+        <v>-44.18582415868082</v>
       </c>
       <c r="F97">
-        <v>-3.281053256871777</v>
+        <v>-4.968516351277636</v>
       </c>
       <c r="G97">
-        <v>-0.8333012018750554</v>
+        <v>-7.943232544065635</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.266458749955778</v>
       </c>
       <c r="E98">
-        <v>-40.97946304415687</v>
+        <v>-44.17314216722234</v>
       </c>
       <c r="F98">
-        <v>-3.139970691031382</v>
+        <v>-4.706800297302355</v>
       </c>
       <c r="G98">
-        <v>-1.47098364340222</v>
+        <v>-7.311941922136269</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.296545356206837</v>
       </c>
       <c r="E99">
-        <v>-43.24943309608576</v>
+        <v>-45.80436643189532</v>
       </c>
       <c r="F99">
-        <v>-3.387037895855557</v>
+        <v>-4.87831293968459</v>
       </c>
       <c r="G99">
-        <v>-1.292593470879889</v>
+        <v>-8.430234729139979</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.353165513305538</v>
       </c>
       <c r="E100">
-        <v>-45.00811579017863</v>
+        <v>-48.62512345619214</v>
       </c>
       <c r="F100">
-        <v>-3.181390717906163</v>
+        <v>-4.382560728498572</v>
       </c>
       <c r="G100">
-        <v>-1.938797244796931</v>
+        <v>-7.321798711700841</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.414755128921395</v>
       </c>
       <c r="E101">
-        <v>-47.30167013473946</v>
+        <v>-49.27681841487298</v>
       </c>
       <c r="F101">
-        <v>-3.551286584482643</v>
+        <v>-5.468600095612892</v>
       </c>
       <c r="G101">
-        <v>-2.30049942218076</v>
+        <v>-7.750703587843657</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.469343265090165</v>
       </c>
       <c r="E102">
-        <v>-50.38090000209058</v>
+        <v>-52.33696868911128</v>
       </c>
       <c r="F102">
-        <v>-3.212225037740569</v>
+        <v>-4.964074645263825</v>
       </c>
       <c r="G102">
-        <v>-2.20506837434587</v>
+        <v>-8.276686685044204</v>
       </c>
     </row>
   </sheetData>
